--- a/data/trans_bre/P44D-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P44D-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>7,2</t>
+          <t>2,17</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>372,54%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-66,87; -2,97</t>
+          <t>-64,63; -1,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-14,28; 49,26</t>
+          <t>-15,95; 48,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 16,26</t>
+          <t>-5,82; 9,56</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,38</t>
+          <t>-100,0; 71,54</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-75,11; 792,9</t>
+          <t>-100,0; 906,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-17,36; 7943,23</t>
+          <t>-57,16; 273,15</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-5,22</t>
+          <t>-6,02</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-39,48%</t>
+          <t>-43,02%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 45,23</t>
+          <t>3,03; 44,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-36,04; -4,59</t>
+          <t>-37,48; -5,53</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-10,86; 0,47</t>
+          <t>-11,9; -0,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-34,62; —</t>
+          <t>-40,0; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -6,45</t>
+          <t>-100,0; -7,46</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-65,67; 4,96</t>
+          <t>-66,23; -2,0</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-1,62</t>
+          <t>-1,49</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-16,44%</t>
+          <t>-15,64%</t>
         </is>
       </c>
     </row>
@@ -794,17 +794,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-19,75; 15,82</t>
+          <t>-17,32; 14,96</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,4; 29,76</t>
+          <t>-3,88; 27,41</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 2,84</t>
+          <t>-6,71; 3,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -814,12 +814,12 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-53,12; 42,02</t>
+          <t>-51,47; 50,48</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-1,05</t>
+          <t>-1,25</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-20,5%</t>
+          <t>-24,49%</t>
         </is>
       </c>
     </row>
@@ -874,17 +874,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 31,12</t>
+          <t>-9,14; 31,75</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-9,3; 15,11</t>
+          <t>-9,01; 15,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 3,23</t>
+          <t>-6,75; 2,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-74,59; 128,0</t>
+          <t>-77,98; 96,38</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,69</t>
+          <t>-2,56</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>-26,02%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 16,28</t>
+          <t>-5,21; 16,02</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,34; 5,69</t>
+          <t>-11,34; 6,77</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-3,48; 5,77</t>
+          <t>-5,35; 0,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-35,66; 218,21</t>
+          <t>-32,65; 213,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-62,29; 61,65</t>
+          <t>-64,23; 66,63</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-34,48; 186,95</t>
+          <t>-46,64; 1,34</t>
         </is>
       </c>
     </row>
